--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9154,0.0054,0.0961,0.0021</t>
-  </si>
-  <si>
-    <t>0.7681,0.0023,0.0077,0.3168</t>
-  </si>
-  <si>
-    <t>0.9191,0.0030,0.0053,0.0524</t>
-  </si>
-  <si>
-    <t>0.9811,0.0001,0.0005,0.0102</t>
-  </si>
-  <si>
-    <t>0.9630,0.0003,0.0004,0.0556</t>
-  </si>
-  <si>
-    <t>0.9131,0.0026,0.0016,0.0680</t>
-  </si>
-  <si>
-    <t>0.9085,0.0134,0.0053,0.0193</t>
-  </si>
-  <si>
-    <t>0.9686,0.0009,0.0002,0.0242</t>
-  </si>
-  <si>
-    <t>0.9183,0.0007,0.0010,0.1506</t>
-  </si>
-  <si>
-    <t>0.8843,0.0100,0.0022,0.0431</t>
-  </si>
-  <si>
-    <t>0.8875,0.0085,0.0055,0.0672</t>
-  </si>
-  <si>
-    <t>0.9674,0.0033,0.0009,0.0106</t>
-  </si>
-  <si>
-    <t>0.9897,0.0002,0.0083,0.0001</t>
-  </si>
-  <si>
-    <t>0.9565,0.0025,0.0417,0.0012</t>
-  </si>
-  <si>
-    <t>0.9823,0.0003,0.0334,0.0001</t>
-  </si>
-  <si>
-    <t>0.9463,0.0014,0.0880,0.0005</t>
-  </si>
-  <si>
-    <t>0.9937,0.0001,0.0023,0.0003</t>
-  </si>
-  <si>
-    <t>0.8555,0.0792,0.0240,0.0017</t>
-  </si>
-  <si>
-    <t>0.8907,0.0360,0.0317,0.0041</t>
-  </si>
-  <si>
-    <t>0.9598,0.0158,0.0105,0.0022</t>
-  </si>
-  <si>
-    <t>0.9524,0.0117,0.0244,0.0011</t>
-  </si>
-  <si>
-    <t>0.6099,0.3301,0.0468,0.0019</t>
-  </si>
-  <si>
-    <t>0.8161,0.0004,0.2506,0.0010</t>
-  </si>
-  <si>
-    <t>0.9719,0.0006,0.0212,0.0006</t>
-  </si>
-  <si>
-    <t>0.2043,0.0112,0.9192,0.0003</t>
-  </si>
-  <si>
-    <t>0.7920,0.0028,0.2699,0.0029</t>
-  </si>
-  <si>
-    <t>0.7506,0.0023,0.5061,0.0006</t>
-  </si>
-  <si>
-    <t>0.8179,0.0315,0.2138,0.0038</t>
-  </si>
-  <si>
-    <t>0.0045,0.0063,0.9937,0.0019</t>
-  </si>
-  <si>
-    <t>0.9839,0.0023,0.0047,0.0008</t>
-  </si>
-  <si>
-    <t>0.9759,0.0055,0.0031,0.0027</t>
-  </si>
-  <si>
-    <t>0.0156,0.0796,0.9906,0.0011</t>
-  </si>
-  <si>
-    <t>0.7199,0.1042,0.1304,0.0034</t>
-  </si>
-  <si>
-    <t>0.9872,0.0004,0.0005,0.0039</t>
-  </si>
-  <si>
-    <t>0.9081,0.0265,0.0390,0.0105</t>
-  </si>
-  <si>
-    <t>0.8893,0.0524,0.0317,0.0040</t>
-  </si>
-  <si>
-    <t>0.9668,0.0105,0.0070,0.0016</t>
-  </si>
-  <si>
-    <t>0.8814,0.0338,0.0415,0.0007</t>
-  </si>
-  <si>
-    <t>0.9659,0.0005,0.0567,0.0002</t>
-  </si>
-  <si>
-    <t>0.1901,0.0009,0.9360,0.0001</t>
-  </si>
-  <si>
-    <t>0.8885,0.0007,0.1885,0.0005</t>
-  </si>
-  <si>
-    <t>0.9034,0.0023,0.1882,0.0002</t>
-  </si>
-  <si>
-    <t>0.0185,0.4223,0.7523,0.0005</t>
-  </si>
-  <si>
-    <t>0.9150,0.0011,0.1620,0.0003</t>
-  </si>
-  <si>
-    <t>0.9814,0.0011,0.0042,0.0026</t>
-  </si>
-  <si>
-    <t>0.9475,0.0093,0.0147,0.0028</t>
-  </si>
-  <si>
-    <t>0.9737,0.0027,0.0144,0.0003</t>
-  </si>
-  <si>
-    <t>0.9642,0.0182,0.0036,0.0003</t>
-  </si>
-  <si>
-    <t>0.2415,0.0617,0.8681,0.0016</t>
-  </si>
-  <si>
-    <t>0.5528,0.0033,0.7138,0.0002</t>
-  </si>
-  <si>
-    <t>0.7871,0.0109,0.3647,0.0019</t>
-  </si>
-  <si>
-    <t>0.1110,0.0036,0.9089,0.0039</t>
-  </si>
-  <si>
-    <t>0.1803,0.0184,0.9266,0.0005</t>
-  </si>
-  <si>
-    <t>0.0598,0.0428,0.9612,0.0003</t>
-  </si>
-  <si>
-    <t>0.9622,0.0027,0.0021,0.0148</t>
-  </si>
-  <si>
-    <t>0.9168,0.0038,0.0091,0.0584</t>
-  </si>
-  <si>
-    <t>0.9655,0.0036,0.0025,0.0119</t>
-  </si>
-  <si>
-    <t>0.2858,0.2573,0.6787,0.0168</t>
-  </si>
-  <si>
-    <t>0.9263,0.0015,0.0014,0.0918</t>
-  </si>
-  <si>
-    <t>0.9565,0.0010,0.0003,0.0402</t>
-  </si>
-  <si>
-    <t>0.9444,0.0053,0.0050,0.0242</t>
-  </si>
-  <si>
-    <t>0.1580,0.3213,0.8050,0.0032</t>
-  </si>
-  <si>
-    <t>0.2565,0.0018,0.9420,0.0000</t>
-  </si>
-  <si>
-    <t>0.3559,0.0041,0.8448,0.0003</t>
-  </si>
-  <si>
-    <t>0.0093,0.2706,0.9904,0.0002</t>
-  </si>
-  <si>
-    <t>0.0130,0.0046,0.9902,0.0002</t>
-  </si>
-  <si>
-    <t>0.9415,0.0306,0.0088,0.0005</t>
-  </si>
-  <si>
-    <t>0.1357,0.9214,0.0117,0.0004</t>
-  </si>
-  <si>
-    <t>0.9739,0.0006,0.0050,0.0031</t>
-  </si>
-  <si>
-    <t>0.9470,0.0048,0.0335,0.0024</t>
-  </si>
-  <si>
-    <t>0.0060,0.3464,0.9703,0.0018</t>
-  </si>
-  <si>
-    <t>0.2451,0.1711,0.6808,0.0006</t>
-  </si>
-  <si>
-    <t>0.6868,0.0286,0.4548,0.0003</t>
-  </si>
-  <si>
-    <t>0.0269,0.9628,0.0848,0.0001</t>
-  </si>
-  <si>
-    <t>0.0141,0.8605,0.8767,0.0015</t>
-  </si>
-  <si>
-    <t>0.4871,0.0012,0.0256,0.4285</t>
-  </si>
-  <si>
-    <t>0.7081,0.0001,0.0009,0.4457</t>
-  </si>
-  <si>
-    <t>0.7551,0.0001,0.0003,0.5133</t>
-  </si>
-  <si>
-    <t>0.7578,0.0001,0.0013,0.3685</t>
-  </si>
-  <si>
-    <t>0.9713,0.0007,0.0022,0.0124</t>
-  </si>
-  <si>
-    <t>0.9639,0.0001,0.0003,0.0564</t>
-  </si>
-  <si>
-    <t>0.0607,0.3244,0.9541,0.0018</t>
-  </si>
-  <si>
-    <t>0.1764,0.0512,0.9058,0.0005</t>
-  </si>
-  <si>
-    <t>0.5792,0.0365,0.4907,0.0014</t>
-  </si>
-  <si>
-    <t>0.1832,0.0493,0.8808,0.0013</t>
-  </si>
-  <si>
-    <t>0.0918,0.2633,0.8441,0.0003</t>
-  </si>
-  <si>
-    <t>0.0177,0.3583,0.9758,0.0012</t>
-  </si>
-  <si>
-    <t>0.8615,0.0193,0.0126,0.0538</t>
-  </si>
-  <si>
-    <t>0.9608,0.0038,0.0035,0.0123</t>
-  </si>
-  <si>
-    <t>0.9818,0.0008,0.0004,0.0120</t>
-  </si>
-  <si>
-    <t>0.8565,0.0025,0.0057,0.1372</t>
-  </si>
-  <si>
-    <t>0.9595,0.0075,0.0072,0.0095</t>
-  </si>
-  <si>
-    <t>0.9110,0.0058,0.0043,0.0666</t>
-  </si>
-  <si>
-    <t>0.9521,0.0010,0.0019,0.0392</t>
-  </si>
-  <si>
-    <t>0.9153,0.0219,0.0147,0.0109</t>
-  </si>
-  <si>
-    <t>0.9704,0.0011,0.0010,0.0220</t>
-  </si>
-  <si>
-    <t>0.9671,0.0004,0.0002,0.0416</t>
-  </si>
-  <si>
-    <t>0.9436,0.0009,0.0003,0.0674</t>
-  </si>
-  <si>
-    <t>0.9578,0.0007,0.0003,0.0519</t>
-  </si>
-  <si>
-    <t>0.8444,0.0027,0.0025,0.1940</t>
-  </si>
-  <si>
-    <t>0.8790,0.0033,0.0079,0.0990</t>
-  </si>
-  <si>
-    <t>0.9062,0.0023,0.0009,0.0844</t>
-  </si>
-  <si>
-    <t>0.9531,0.0007,0.0007,0.0738</t>
-  </si>
-  <si>
-    <t>0.0140,0.0044,0.9947,0.0008</t>
-  </si>
-  <si>
-    <t>0.5679,0.0385,0.5500,0.0037</t>
-  </si>
-  <si>
-    <t>0.9223,0.0027,0.0741,0.0022</t>
-  </si>
-  <si>
-    <t>0.9729,0.0005,0.0317,0.0004</t>
-  </si>
-  <si>
-    <t>0.6745,0.2274,0.0899,0.0057</t>
-  </si>
-  <si>
-    <t>0.7682,0.1535,0.0170,0.0038</t>
-  </si>
-  <si>
-    <t>0.7330,0.1765,0.0318,0.0057</t>
-  </si>
-  <si>
-    <t>0.8402,0.0567,0.0420,0.0081</t>
-  </si>
-  <si>
-    <t>0.8590,0.0940,0.0140,0.0029</t>
-  </si>
-  <si>
-    <t>0.5474,0.2871,0.1290,0.0218</t>
-  </si>
-  <si>
-    <t>0.9259,0.0105,0.0167,0.0115</t>
-  </si>
-  <si>
-    <t>0.9724,0.0007,0.0123,0.0010</t>
-  </si>
-  <si>
-    <t>0.9458,0.0033,0.0657,0.0007</t>
-  </si>
-  <si>
-    <t>0.9717,0.0011,0.0201,0.0009</t>
-  </si>
-  <si>
-    <t>0.9898,0.0003,0.0079,0.0002</t>
-  </si>
-  <si>
-    <t>0.9518,0.0043,0.0107,0.0079</t>
-  </si>
-  <si>
-    <t>0.9869,0.0036,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9817,0.0047,0.0028,0.0005</t>
-  </si>
-  <si>
-    <t>0.9015,0.0310,0.0353,0.0035</t>
-  </si>
-  <si>
-    <t>0.1812,0.6828,0.2702,0.0011</t>
-  </si>
-  <si>
-    <t>0.8100,0.0866,0.0339,0.0186</t>
-  </si>
-  <si>
-    <t>0.9149,0.0170,0.0288,0.0075</t>
-  </si>
-  <si>
-    <t>0.9108,0.0152,0.0494,0.0051</t>
-  </si>
-  <si>
-    <t>0.9883,0.0006,0.0019,0.0022</t>
-  </si>
-  <si>
-    <t>0.9500,0.0029,0.0013,0.0284</t>
-  </si>
-  <si>
-    <t>0.8828,0.0042,0.0025,0.1111</t>
-  </si>
-  <si>
-    <t>0.9780,0.0036,0.0061,0.0027</t>
-  </si>
-  <si>
-    <t>0.9442,0.0032,0.0008,0.0278</t>
-  </si>
-  <si>
-    <t>0.9941,0.0004,0.0005,0.0013</t>
-  </si>
-  <si>
-    <t>0.9198,0.0023,0.0032,0.0757</t>
-  </si>
-  <si>
-    <t>0.9284,0.0047,0.0066,0.0402</t>
-  </si>
-  <si>
-    <t>0.7715,0.0133,0.4120,0.0003</t>
-  </si>
-  <si>
-    <t>0.6718,0.0285,0.3690,0.0004</t>
-  </si>
-  <si>
-    <t>0.1319,0.0583,0.8804,0.0014</t>
-  </si>
-  <si>
-    <t>0.6333,0.0065,0.6485,0.0003</t>
-  </si>
-  <si>
-    <t>0.9952,0.0002,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9681,0.0007,0.0103,0.0025</t>
-  </si>
-  <si>
-    <t>0.9781,0.0003,0.0175,0.0006</t>
-  </si>
-  <si>
-    <t>0.9900,0.0004,0.0044,0.0003</t>
-  </si>
-  <si>
-    <t>0.9228,0.0008,0.0045,0.0550</t>
-  </si>
-  <si>
-    <t>0.5673,0.0004,0.0040,0.5869</t>
-  </si>
-  <si>
-    <t>0.7985,0.0003,0.0021,0.2475</t>
-  </si>
-  <si>
-    <t>0.9115,0.0002,0.0018,0.0752</t>
-  </si>
-  <si>
-    <t>0.0454,0.5298,0.8067,0.0105</t>
-  </si>
-  <si>
-    <t>0.9179,0.0039,0.0064,0.0361</t>
-  </si>
-  <si>
-    <t>0.9892,0.0010,0.0011,0.0013</t>
-  </si>
-  <si>
-    <t>0.9548,0.0019,0.0065,0.0175</t>
-  </si>
-  <si>
-    <t>0.8752,0.0078,0.0127,0.0610</t>
-  </si>
-  <si>
-    <t>0.9823,0.0010,0.0005,0.0057</t>
-  </si>
-  <si>
-    <t>0.9677,0.0004,0.0004,0.0379</t>
-  </si>
-  <si>
-    <t>0.8105,0.0010,0.0004,0.2257</t>
-  </si>
-  <si>
-    <t>0.1704,0.0412,0.8760,0.0281</t>
-  </si>
-  <si>
-    <t>0.7519,0.0029,0.0096,0.2087</t>
-  </si>
-  <si>
-    <t>0.9834,0.0004,0.0005,0.0084</t>
-  </si>
-  <si>
-    <t>0.9708,0.0038,0.0126,0.0009</t>
-  </si>
-  <si>
-    <t>0.9775,0.0003,0.0038,0.0045</t>
-  </si>
-  <si>
-    <t>0.9450,0.0070,0.0200,0.0042</t>
-  </si>
-  <si>
-    <t>0.9629,0.0051,0.0088,0.0031</t>
-  </si>
-  <si>
-    <t>0.9385,0.0066,0.0121,0.0082</t>
-  </si>
-  <si>
-    <t>0.9882,0.0007,0.0039,0.0010</t>
-  </si>
-  <si>
-    <t>0.9182,0.0044,0.0016,0.0510</t>
-  </si>
-  <si>
-    <t>0.9568,0.0013,0.0007,0.0442</t>
-  </si>
-  <si>
-    <t>0.8875,0.0008,0.0016,0.1887</t>
-  </si>
-  <si>
-    <t>0.9675,0.0005,0.0010,0.0419</t>
-  </si>
-  <si>
-    <t>0.9668,0.0060,0.0012,0.0082</t>
-  </si>
-  <si>
-    <t>0.8478,0.0135,0.0090,0.0665</t>
-  </si>
-  <si>
-    <t>0.8656,0.0010,0.0008,0.2016</t>
-  </si>
-  <si>
-    <t>0.9260,0.0036,0.0080,0.0415</t>
-  </si>
-  <si>
-    <t>0.9714,0.0027,0.0041,0.0033</t>
-  </si>
-  <si>
-    <t>0.8534,0.0077,0.0029,0.0779</t>
-  </si>
-  <si>
-    <t>0.9267,0.0150,0.0181,0.0051</t>
-  </si>
-  <si>
-    <t>0.9354,0.0107,0.0127,0.0132</t>
-  </si>
-  <si>
-    <t>0.9200,0.0091,0.0020,0.0232</t>
-  </si>
-  <si>
-    <t>0.9582,0.0017,0.0050,0.0199</t>
-  </si>
-  <si>
-    <t>0.9902,0.0005,0.0002,0.0032</t>
-  </si>
-  <si>
-    <t>0.9246,0.0020,0.0061,0.0667</t>
-  </si>
-  <si>
-    <t>0.0051,0.0429,0.9932,0.0006</t>
-  </si>
-  <si>
-    <t>0.9745,0.0018,0.0026,0.0092</t>
-  </si>
-  <si>
-    <t>0.0022,0.0017,0.9977,0.0002</t>
-  </si>
-  <si>
-    <t>0.6115,0.0076,0.6534,0.0009</t>
-  </si>
-  <si>
-    <t>0.9359,0.0007,0.1435,0.0002</t>
-  </si>
-  <si>
-    <t>0.2191,0.0157,0.9325,0.0003</t>
-  </si>
-  <si>
-    <t>0.5463,0.0092,0.6277,0.0013</t>
-  </si>
-  <si>
-    <t>0.7302,0.0029,0.4219,0.0012</t>
-  </si>
-  <si>
-    <t>0.7436,0.0050,0.4374,0.0013</t>
-  </si>
-  <si>
-    <t>0.7610,0.0066,0.3320,0.0057</t>
-  </si>
-  <si>
-    <t>0.9870,0.0004,0.0118,0.0003</t>
-  </si>
-  <si>
-    <t>0.8919,0.0059,0.0962,0.0030</t>
-  </si>
-  <si>
-    <t>0.9649,0.0015,0.0298,0.0005</t>
-  </si>
-  <si>
-    <t>0.8915,0.0043,0.1125,0.0027</t>
-  </si>
-  <si>
-    <t>0.9647,0.0008,0.0416,0.0005</t>
-  </si>
-  <si>
-    <t>0.9644,0.0007,0.0292,0.0013</t>
-  </si>
-  <si>
-    <t>0.9475,0.0010,0.0159,0.0073</t>
-  </si>
-  <si>
-    <t>0.8679,0.0128,0.0115,0.0540</t>
-  </si>
-  <si>
-    <t>0.9779,0.0082,0.0010,0.0010</t>
-  </si>
-  <si>
-    <t>0.8601,0.0435,0.0465,0.0260</t>
-  </si>
-  <si>
-    <t>0.9577,0.0018,0.0025,0.0235</t>
-  </si>
-  <si>
-    <t>0.8860,0.0057,0.0037,0.0819</t>
-  </si>
-  <si>
-    <t>0.9852,0.0005,0.0108,0.0003</t>
-  </si>
-  <si>
-    <t>0.9713,0.0015,0.0227,0.0006</t>
-  </si>
-  <si>
-    <t>0.9792,0.0004,0.0095,0.0012</t>
-  </si>
-  <si>
-    <t>0.9805,0.0006,0.0180,0.0002</t>
-  </si>
-  <si>
-    <t>0.9577,0.0007,0.0262,0.0026</t>
-  </si>
-  <si>
-    <t>0.0516,0.0174,0.9391,0.0119</t>
-  </si>
-  <si>
-    <t>0.6982,0.0115,0.4275,0.0023</t>
-  </si>
-  <si>
-    <t>0.0763,0.0006,0.9748,0.0001</t>
-  </si>
-  <si>
-    <t>0.6081,0.0030,0.5028,0.0019</t>
-  </si>
-  <si>
-    <t>0.2200,0.0088,0.8455,0.0007</t>
-  </si>
-  <si>
-    <t>0.8425,0.0047,0.0039,0.1765</t>
-  </si>
-  <si>
-    <t>0.9439,0.0055,0.0021,0.0215</t>
-  </si>
-  <si>
-    <t>0.9519,0.0028,0.0009,0.0215</t>
-  </si>
-  <si>
-    <t>0.8726,0.0005,0.0012,0.2494</t>
-  </si>
-  <si>
-    <t>0.9487,0.0020,0.0016,0.0429</t>
-  </si>
-  <si>
-    <t>0.8814,0.0059,0.0014,0.0487</t>
-  </si>
-  <si>
-    <t>0.9154,0.0067,0.0021,0.0341</t>
-  </si>
-  <si>
-    <t>0.9194,0.0006,0.0007,0.1409</t>
-  </si>
-  <si>
-    <t>0.3191,0.0086,0.7968,0.0066</t>
-  </si>
-  <si>
-    <t>0.8134,0.0056,0.2428,0.0049</t>
-  </si>
-  <si>
-    <t>0.9547,0.0107,0.0142,0.0037</t>
-  </si>
-  <si>
-    <t>0.5956,0.0015,0.6549,0.0005</t>
-  </si>
-  <si>
-    <t>0.0025,0.0078,0.9944,0.0002</t>
-  </si>
-  <si>
-    <t>0.9124,0.0019,0.1178,0.0005</t>
-  </si>
-  <si>
-    <t>0.0191,0.0107,0.9916,0.0001</t>
-  </si>
-  <si>
-    <t>0.9195,0.0022,0.1341,0.0006</t>
-  </si>
-  <si>
-    <t>0.0357,0.0097,0.9734,0.0009</t>
-  </si>
-  <si>
-    <t>0.4306,0.0049,0.7473,0.0013</t>
-  </si>
-  <si>
-    <t>0.4215,0.0138,0.6835,0.0078</t>
-  </si>
-  <si>
-    <t>0.9692,0.0010,0.0311,0.0004</t>
-  </si>
-  <si>
-    <t>0.9663,0.0013,0.0234,0.0017</t>
-  </si>
-  <si>
-    <t>0.9865,0.0003,0.0096,0.0004</t>
-  </si>
-  <si>
-    <t>0.7671,0.0581,0.0146,0.0346</t>
-  </si>
-  <si>
-    <t>0.9774,0.0009,0.0014,0.0099</t>
-  </si>
-  <si>
-    <t>0.9221,0.0036,0.0011,0.0536</t>
-  </si>
-  <si>
-    <t>0.9718,0.0016,0.0023,0.0129</t>
-  </si>
-  <si>
-    <t>0.9854,0.0005,0.0005,0.0088</t>
-  </si>
-  <si>
-    <t>0.8783,0.0090,0.0039,0.0511</t>
-  </si>
-  <si>
-    <t>0.9770,0.0008,0.0007,0.0175</t>
-  </si>
-  <si>
-    <t>0.9776,0.0004,0.0002,0.0233</t>
-  </si>
-  <si>
-    <t>0.9301,0.0004,0.1652,0.0002</t>
-  </si>
-  <si>
-    <t>0.1882,0.0172,0.9298,0.0004</t>
-  </si>
-  <si>
-    <t>0.1012,0.0307,0.9615,0.0005</t>
-  </si>
-  <si>
-    <t>0.8998,0.0067,0.1175,0.0030</t>
-  </si>
-  <si>
-    <t>0.7881,0.0223,0.2425,0.0015</t>
-  </si>
-  <si>
-    <t>0.9716,0.0005,0.0153,0.0013</t>
-  </si>
-  <si>
-    <t>0.7112,0.0030,0.4871,0.0009</t>
-  </si>
-  <si>
-    <t>0.1020,0.0071,0.9202,0.0028</t>
-  </si>
-  <si>
-    <t>0.9181,0.0002,0.0018,0.0622</t>
-  </si>
-  <si>
-    <t>0.9094,0.0004,0.0221,0.0137</t>
-  </si>
-  <si>
-    <t>0.9281,0.0001,0.0004,0.0996</t>
-  </si>
-  <si>
-    <t>0.7914,0.0001,0.0015,0.2491</t>
-  </si>
-  <si>
-    <t>0.6836,0.0002,0.0014,0.5298</t>
-  </si>
-  <si>
-    <t>0.8628,0.0126,0.0809,0.0150</t>
+    <t>0.9133,0.0153,0.0104,0.0610</t>
+  </si>
+  <si>
+    <t>0.0209,0.0015,0.0002,0.9942</t>
+  </si>
+  <si>
+    <t>0.9701,0.0037,0.0051,0.0150</t>
+  </si>
+  <si>
+    <t>0.1530,0.0080,0.0009,0.9252</t>
+  </si>
+  <si>
+    <t>0.9976,0.0007,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9974,0.0015,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9973,0.0004,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0000,0.0014</t>
+  </si>
+  <si>
+    <t>0.9973,0.0010,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9970,0.0010,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9972,0.0007,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9376,0.0009,0.1460,0.0003</t>
+  </si>
+  <si>
+    <t>0.0162,0.0052,0.9814,0.0013</t>
+  </si>
+  <si>
+    <t>0.6418,0.0126,0.6312,0.0009</t>
+  </si>
+  <si>
+    <t>0.5637,0.0051,0.6033,0.0003</t>
+  </si>
+  <si>
+    <t>0.9416,0.0041,0.0429,0.0027</t>
+  </si>
+  <si>
+    <t>0.0004,0.9985,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9988,0.0021,0.0009</t>
+  </si>
+  <si>
+    <t>0.7693,0.2744,0.0139,0.0025</t>
+  </si>
+  <si>
+    <t>0.0004,0.9975,0.0027,0.0017</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.4505,0.0078,0.6555,0.0044</t>
+  </si>
+  <si>
+    <t>0.5226,0.0123,0.5597,0.0098</t>
+  </si>
+  <si>
+    <t>0.0012,0.0006,0.9974,0.0005</t>
+  </si>
+  <si>
+    <t>0.3492,0.0027,0.7757,0.0009</t>
+  </si>
+  <si>
+    <t>0.1751,0.0006,0.9417,0.0002</t>
+  </si>
+  <si>
+    <t>0.0139,0.0013,0.9879,0.0010</t>
+  </si>
+  <si>
+    <t>0.0022,0.0009,0.9963,0.0010</t>
+  </si>
+  <si>
+    <t>0.0567,0.8175,0.2064,0.0120</t>
+  </si>
+  <si>
+    <t>0.7423,0.1344,0.1217,0.0031</t>
+  </si>
+  <si>
+    <t>0.0039,0.0157,0.9944,0.0071</t>
+  </si>
+  <si>
+    <t>0.0133,0.8392,0.2128,0.0008</t>
+  </si>
+  <si>
+    <t>0.6519,0.3702,0.0312,0.0212</t>
+  </si>
+  <si>
+    <t>0.2637,0.0841,0.7144,0.0828</t>
+  </si>
+  <si>
+    <t>0.6093,0.4960,0.0054,0.0027</t>
+  </si>
+  <si>
+    <t>0.0032,0.9918,0.0978,0.0019</t>
+  </si>
+  <si>
+    <t>0.0082,0.9629,0.0263,0.0106</t>
+  </si>
+  <si>
+    <t>0.0277,0.0068,0.9613,0.0081</t>
+  </si>
+  <si>
+    <t>0.1562,0.0458,0.8092,0.0102</t>
+  </si>
+  <si>
+    <t>0.0004,0.0005,0.9971,0.0056</t>
+  </si>
+  <si>
+    <t>0.0088,0.0437,0.9818,0.0007</t>
+  </si>
+  <si>
+    <t>0.0028,0.9846,0.0511,0.0003</t>
+  </si>
+  <si>
+    <t>0.0042,0.0037,0.9938,0.0005</t>
+  </si>
+  <si>
+    <t>0.0670,0.1395,0.0037,0.8646</t>
+  </si>
+  <si>
+    <t>0.0039,0.9857,0.0163,0.0067</t>
+  </si>
+  <si>
+    <t>0.0136,0.9792,0.0101,0.0013</t>
+  </si>
+  <si>
+    <t>0.0011,0.9966,0.0230,0.0011</t>
+  </si>
+  <si>
+    <t>0.0018,0.4027,0.9697,0.0037</t>
+  </si>
+  <si>
+    <t>0.0028,0.1178,0.9873,0.0010</t>
+  </si>
+  <si>
+    <t>0.0014,0.0009,0.9960,0.0034</t>
+  </si>
+  <si>
+    <t>0.0031,0.0013,0.9952,0.0008</t>
+  </si>
+  <si>
+    <t>0.0042,0.0027,0.9931,0.0011</t>
+  </si>
+  <si>
+    <t>0.0035,0.0220,0.9768,0.0023</t>
+  </si>
+  <si>
+    <t>0.9845,0.0204,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9922,0.0042,0.0015,0.0012</t>
+  </si>
+  <si>
+    <t>0.9968,0.0013,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.0005,0.0489,0.9958,0.0653</t>
+  </si>
+  <si>
+    <t>0.9955,0.0012,0.0023,0.0004</t>
+  </si>
+  <si>
+    <t>0.9909,0.0091,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.9755,0.0328,0.0015,0.0009</t>
+  </si>
+  <si>
+    <t>0.0012,0.7996,0.9845,0.0003</t>
+  </si>
+  <si>
+    <t>0.1374,0.0058,0.9213,0.0012</t>
+  </si>
+  <si>
+    <t>0.0138,0.0419,0.9690,0.0080</t>
+  </si>
+  <si>
+    <t>0.0003,0.9792,0.9865,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.0008,0.9983,0.0003</t>
+  </si>
+  <si>
+    <t>0.0053,0.9900,0.0106,0.0004</t>
+  </si>
+  <si>
+    <t>0.0058,0.9870,0.0058,0.0010</t>
+  </si>
+  <si>
+    <t>0.7626,0.0180,0.3794,0.0046</t>
+  </si>
+  <si>
+    <t>0.8086,0.0202,0.2922,0.0045</t>
+  </si>
+  <si>
+    <t>0.0024,0.0087,0.9928,0.0109</t>
+  </si>
+  <si>
+    <t>0.0001,0.9960,0.9406,0.0002</t>
+  </si>
+  <si>
+    <t>0.0065,0.8491,0.8222,0.0012</t>
+  </si>
+  <si>
+    <t>0.0036,0.9889,0.1210,0.0013</t>
+  </si>
+  <si>
+    <t>0.0007,0.9431,0.9693,0.0003</t>
+  </si>
+  <si>
+    <t>0.0092,0.0002,0.0016,0.9949</t>
+  </si>
+  <si>
+    <t>0.0007,0.0026,0.0003,0.9992</t>
+  </si>
+  <si>
+    <t>0.0021,0.0002,0.0007,0.9983</t>
+  </si>
+  <si>
+    <t>0.0079,0.0002,0.0002,0.9976</t>
+  </si>
+  <si>
+    <t>0.0032,0.0006,0.0011,0.9981</t>
+  </si>
+  <si>
+    <t>0.0015,0.0071,0.0005,0.9983</t>
+  </si>
+  <si>
+    <t>0.0006,0.9754,0.9773,0.0005</t>
+  </si>
+  <si>
+    <t>0.0019,0.2901,0.9939,0.0004</t>
+  </si>
+  <si>
+    <t>0.0077,0.9526,0.0827,0.0006</t>
+  </si>
+  <si>
+    <t>0.0006,0.1653,0.9937,0.0004</t>
+  </si>
+  <si>
+    <t>0.0012,0.9762,0.6334,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9403,0.9667,0.0003</t>
+  </si>
+  <si>
+    <t>0.9976,0.0011,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9814,0.0070,0.0098,0.0024</t>
+  </si>
+  <si>
+    <t>0.9934,0.0069,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9950,0.0009,0.0004,0.0020</t>
+  </si>
+  <si>
+    <t>0.9985,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9917,0.0067,0.0013,0.0009</t>
+  </si>
+  <si>
+    <t>0.9974,0.0020,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9973,0.0005,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9978,0.0005,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9981,0.0009,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.0166,0.0016,0.9913,0.0008</t>
+  </si>
+  <si>
+    <t>0.0748,0.0072,0.9417,0.0030</t>
+  </si>
+  <si>
+    <t>0.8553,0.0051,0.0480,0.0409</t>
+  </si>
+  <si>
+    <t>0.0088,0.0009,0.9893,0.0027</t>
+  </si>
+  <si>
+    <t>0.0036,0.9917,0.0006,0.0031</t>
+  </si>
+  <si>
+    <t>0.0043,0.9932,0.0048,0.0007</t>
+  </si>
+  <si>
+    <t>0.0356,0.9611,0.0047,0.0040</t>
+  </si>
+  <si>
+    <t>0.0188,0.9791,0.0029,0.0006</t>
+  </si>
+  <si>
+    <t>0.0038,0.9945,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.0032,0.9936,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.9737,0.0260,0.0026,0.0009</t>
+  </si>
+  <si>
+    <t>0.5508,0.1586,0.3038,0.0580</t>
+  </si>
+  <si>
+    <t>0.3902,0.0045,0.7875,0.0017</t>
+  </si>
+  <si>
+    <t>0.5311,0.0700,0.3989,0.0728</t>
+  </si>
+  <si>
+    <t>0.8942,0.0113,0.1330,0.0034</t>
+  </si>
+  <si>
+    <t>0.0262,0.1894,0.0175,0.8971</t>
+  </si>
+  <si>
+    <t>0.0009,0.9970,0.0104,0.0006</t>
+  </si>
+  <si>
+    <t>0.0016,0.9903,0.0047,0.0094</t>
+  </si>
+  <si>
+    <t>0.0005,0.9947,0.0040,0.0045</t>
+  </si>
+  <si>
+    <t>0.0001,0.9966,0.7191,0.0006</t>
+  </si>
+  <si>
+    <t>0.0024,0.9941,0.0110,0.0026</t>
+  </si>
+  <si>
+    <t>0.1300,0.8726,0.0080,0.0036</t>
+  </si>
+  <si>
+    <t>0.2559,0.8195,0.0064,0.0018</t>
+  </si>
+  <si>
+    <t>0.9957,0.0012,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9942,0.0015,0.0009,0.0015</t>
+  </si>
+  <si>
+    <t>0.9968,0.0005,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9925,0.0021,0.0022,0.0009</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9866,0.0057,0.0021,0.0026</t>
+  </si>
+  <si>
+    <t>0.9930,0.0011,0.0012,0.0022</t>
+  </si>
+  <si>
+    <t>0.9868,0.0092,0.0040,0.0010</t>
+  </si>
+  <si>
+    <t>0.0011,0.6529,0.9969,0.0007</t>
+  </si>
+  <si>
+    <t>0.0038,0.7427,0.9659,0.0008</t>
+  </si>
+  <si>
+    <t>0.0065,0.0299,0.9871,0.0024</t>
+  </si>
+  <si>
+    <t>0.0552,0.0349,0.8943,0.0018</t>
+  </si>
+  <si>
+    <t>0.9872,0.0019,0.0036,0.0010</t>
+  </si>
+  <si>
+    <t>0.1807,0.0010,0.8949,0.0024</t>
+  </si>
+  <si>
+    <t>0.2139,0.0013,0.9315,0.0009</t>
+  </si>
+  <si>
+    <t>0.7683,0.0314,0.2931,0.0180</t>
+  </si>
+  <si>
+    <t>0.1009,0.0009,0.0029,0.9571</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0002,0.9999</t>
+  </si>
+  <si>
+    <t>0.0019,0.0013,0.0002,0.9990</t>
+  </si>
+  <si>
+    <t>0.0434,0.0003,0.0002,0.9926</t>
+  </si>
+  <si>
+    <t>0.0020,0.9767,0.5554,0.0030</t>
+  </si>
+  <si>
+    <t>0.9968,0.0008,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.0020,0.9911,0.0011,0.0075</t>
+  </si>
+  <si>
+    <t>0.9857,0.0036,0.0042,0.0032</t>
+  </si>
+  <si>
+    <t>0.5343,0.5347,0.0229,0.0047</t>
+  </si>
+  <si>
+    <t>0.9803,0.0080,0.0055,0.0037</t>
+  </si>
+  <si>
+    <t>0.3445,0.0010,0.0025,0.8387</t>
+  </si>
+  <si>
+    <t>0.9930,0.0010,0.0015,0.0017</t>
+  </si>
+  <si>
+    <t>0.0162,0.1812,0.9593,0.0475</t>
+  </si>
+  <si>
+    <t>0.9517,0.0016,0.0029,0.0469</t>
+  </si>
+  <si>
+    <t>0.9761,0.0049,0.0027,0.0133</t>
+  </si>
+  <si>
+    <t>0.7682,0.2351,0.0102,0.0074</t>
+  </si>
+  <si>
+    <t>0.9699,0.0097,0.0106,0.0028</t>
+  </si>
+  <si>
+    <t>0.9336,0.0389,0.0222,0.0054</t>
+  </si>
+  <si>
+    <t>0.0967,0.8922,0.0436,0.0045</t>
+  </si>
+  <si>
+    <t>0.7347,0.1803,0.0390,0.0069</t>
+  </si>
+  <si>
+    <t>0.9704,0.0130,0.0070,0.0024</t>
+  </si>
+  <si>
+    <t>0.9975,0.0006,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9967,0.0004,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9899,0.0021,0.0006,0.0049</t>
+  </si>
+  <si>
+    <t>0.9958,0.0006,0.0011,0.0010</t>
+  </si>
+  <si>
+    <t>0.9832,0.0080,0.0050,0.0032</t>
+  </si>
+  <si>
+    <t>0.9903,0.0054,0.0031,0.0006</t>
+  </si>
+  <si>
+    <t>0.9879,0.0044,0.0013,0.0036</t>
+  </si>
+  <si>
+    <t>0.9897,0.0023,0.0017,0.0034</t>
+  </si>
+  <si>
+    <t>0.8653,0.1579,0.0004,0.0033</t>
+  </si>
+  <si>
+    <t>0.9191,0.1564,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.9280,0.0749,0.0087,0.0023</t>
+  </si>
+  <si>
+    <t>0.9439,0.0180,0.0095,0.0225</t>
+  </si>
+  <si>
+    <t>0.9918,0.0088,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9575,0.0229,0.0077,0.0087</t>
+  </si>
+  <si>
+    <t>0.9939,0.0045,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9539,0.0524,0.0049,0.0011</t>
+  </si>
+  <si>
+    <t>0.0005,0.0066,0.9993,0.0003</t>
+  </si>
+  <si>
+    <t>0.9569,0.0287,0.0083,0.0051</t>
+  </si>
+  <si>
+    <t>0.0024,0.0028,0.9969,0.0002</t>
+  </si>
+  <si>
+    <t>0.0093,0.0834,0.9798,0.0030</t>
+  </si>
+  <si>
+    <t>0.1312,0.0012,0.9557,0.0006</t>
+  </si>
+  <si>
+    <t>0.0424,0.0653,0.9584,0.0014</t>
+  </si>
+  <si>
+    <t>0.0008,0.0007,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0008,0.9980,0.0006</t>
+  </si>
+  <si>
+    <t>0.0006,0.0029,0.9958,0.0020</t>
+  </si>
+  <si>
+    <t>0.1846,0.0328,0.8366,0.0212</t>
+  </si>
+  <si>
+    <t>0.5015,0.0104,0.5853,0.0036</t>
+  </si>
+  <si>
+    <t>0.7185,0.0215,0.3965,0.0025</t>
+  </si>
+  <si>
+    <t>0.0535,0.4794,0.4753,0.0019</t>
+  </si>
+  <si>
+    <t>0.6073,0.1152,0.4117,0.0075</t>
+  </si>
+  <si>
+    <t>0.0714,0.8606,0.1176,0.0667</t>
+  </si>
+  <si>
+    <t>0.7916,0.0083,0.2090,0.0166</t>
+  </si>
+  <si>
+    <t>0.6883,0.0510,0.2774,0.0045</t>
+  </si>
+  <si>
+    <t>0.9695,0.0323,0.0051,0.0007</t>
+  </si>
+  <si>
+    <t>0.2719,0.8454,0.0013,0.0012</t>
+  </si>
+  <si>
+    <t>0.9517,0.0718,0.0024,0.0019</t>
+  </si>
+  <si>
+    <t>0.9748,0.0426,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.0875,0.9427,0.0007,0.0018</t>
+  </si>
+  <si>
+    <t>0.8090,0.0201,0.2469,0.0035</t>
+  </si>
+  <si>
+    <t>0.9852,0.0002,0.0080,0.0011</t>
+  </si>
+  <si>
+    <t>0.6844,0.0038,0.2777,0.0188</t>
+  </si>
+  <si>
+    <t>0.8768,0.0072,0.1525,0.0051</t>
+  </si>
+  <si>
+    <t>0.2829,0.0105,0.6628,0.0636</t>
+  </si>
+  <si>
+    <t>0.0056,0.0042,0.9869,0.0177</t>
+  </si>
+  <si>
+    <t>0.0052,0.0519,0.9678,0.0186</t>
+  </si>
+  <si>
+    <t>0.0050,0.0240,0.9910,0.0012</t>
+  </si>
+  <si>
+    <t>0.0216,0.0426,0.9481,0.0021</t>
+  </si>
+  <si>
+    <t>0.0122,0.0317,0.9576,0.0118</t>
+  </si>
+  <si>
+    <t>0.9970,0.0012,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9935,0.0016,0.0003,0.0018</t>
+  </si>
+  <si>
+    <t>0.9918,0.0053,0.0012,0.0008</t>
+  </si>
+  <si>
+    <t>0.9918,0.0025,0.0034,0.0009</t>
+  </si>
+  <si>
+    <t>0.9872,0.0072,0.0006,0.0028</t>
+  </si>
+  <si>
+    <t>0.9974,0.0008,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9960,0.0016,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9956,0.0008,0.0006,0.0015</t>
+  </si>
+  <si>
+    <t>0.0290,0.0350,0.9809,0.0011</t>
+  </si>
+  <si>
+    <t>0.0425,0.0382,0.9466,0.0063</t>
+  </si>
+  <si>
+    <t>0.7046,0.0149,0.2867,0.0218</t>
+  </si>
+  <si>
+    <t>0.0066,0.0018,0.9907,0.0011</t>
+  </si>
+  <si>
+    <t>0.0026,0.0054,0.9821,0.0040</t>
+  </si>
+  <si>
+    <t>0.0137,0.0688,0.9528,0.0025</t>
+  </si>
+  <si>
+    <t>0.0052,0.0008,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0069,0.0025,0.9871,0.0005</t>
+  </si>
+  <si>
+    <t>0.0044,0.0153,0.9955,0.0005</t>
+  </si>
+  <si>
+    <t>0.0041,0.0013,0.9930,0.0011</t>
+  </si>
+  <si>
+    <t>0.0412,0.0274,0.9478,0.0047</t>
+  </si>
+  <si>
+    <t>0.8009,0.0148,0.2520,0.0121</t>
+  </si>
+  <si>
+    <t>0.9238,0.0014,0.1596,0.0008</t>
+  </si>
+  <si>
+    <t>0.8803,0.0005,0.1303,0.0043</t>
+  </si>
+  <si>
+    <t>0.9941,0.0033,0.0008,0.0011</t>
+  </si>
+  <si>
+    <t>0.9901,0.0062,0.0008,0.0025</t>
+  </si>
+  <si>
+    <t>0.9981,0.0006,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9916,0.0061,0.0014,0.0007</t>
+  </si>
+  <si>
+    <t>0.9969,0.0011,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9900,0.0041,0.0030,0.0013</t>
+  </si>
+  <si>
+    <t>0.9953,0.0029,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9981,0.0005,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0040,0.0038,0.9920,0.0003</t>
+  </si>
+  <si>
+    <t>0.0015,0.0636,0.9876,0.0022</t>
+  </si>
+  <si>
+    <t>0.0159,0.0508,0.9697,0.0076</t>
+  </si>
+  <si>
+    <t>0.0379,0.0149,0.9481,0.0017</t>
+  </si>
+  <si>
+    <t>0.0010,0.0071,0.9972,0.0002</t>
+  </si>
+  <si>
+    <t>0.0085,0.0040,0.9066,0.3430</t>
+  </si>
+  <si>
+    <t>0.1448,0.0109,0.8781,0.0090</t>
+  </si>
+  <si>
+    <t>0.3021,0.0026,0.5268,0.0109</t>
+  </si>
+  <si>
+    <t>0.8221,0.0087,0.0014,0.1924</t>
+  </si>
+  <si>
+    <t>0.0075,0.1427,0.0069,0.9800</t>
+  </si>
+  <si>
+    <t>0.0322,0.0008,0.0004,0.9902</t>
+  </si>
+  <si>
+    <t>0.0013,0.0000,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0009,0.0005,0.0003,0.9994</t>
+  </si>
+  <si>
+    <t>0.9229,0.0034,0.0020,0.0682</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2247,7 +2247,7 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
         <v>285</v>
@@ -2261,7 +2261,7 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
         <v>286</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2429,7 +2429,7 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
         <v>298</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3451,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3521,7 +3521,7 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D114" t="s">
         <v>376</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3689,7 +3689,7 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
         <v>388</v>
@@ -3703,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
         <v>389</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3899,7 +3899,7 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
         <v>403</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4655,7 +4655,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D195" t="s">
         <v>457</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4753,7 +4753,7 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
         <v>464</v>
@@ -4823,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
         <v>469</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
